--- a/reports/SIA_TradeX_Income_Ledger.xlsx
+++ b/reports/SIA_TradeX_Income_Ledger.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="166" formatCode="$#,##0.00"/>
     <numFmt numFmtId="167" formatCode="$#,##0.0000"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,8 +65,14 @@
       <color rgb="00F8FAFC"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00991B1B"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -95,6 +101,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00334155"/>
         <bgColor rgb="00334155"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
     <fill>
@@ -136,12 +148,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -197,6 +209,12 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -601,7 +619,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026, 08:29 PM UTC</t>
+          <t>09 Oct 2026, 08:34 PM UTC</t>
         </is>
       </c>
     </row>
@@ -642,7 +660,7 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1.5</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
@@ -652,7 +670,7 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>1</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
@@ -662,7 +680,7 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>1</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
@@ -672,7 +690,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
@@ -682,7 +700,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>1</v>
+        <v>0.5275590551181102</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
@@ -692,7 +710,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1.5</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
@@ -702,7 +720,7 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.5</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
@@ -740,7 +758,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
     <col width="35" customWidth="1" min="10" max="10"/>
@@ -814,35 +832,35 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1.5</v>
+        <v>2.12</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1.5</v>
+        <v>2.12</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>1</v>
+        <v>127</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>1</v>
+        <v>0.528</v>
       </c>
       <c r="H3" s="11" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I3" s="13" t="n">
-        <v>1001.5</v>
+        <v>997.26</v>
       </c>
       <c r="J3" s="13" t="n">
-        <v>1001.5</v>
+        <v>997.26</v>
       </c>
       <c r="K3" s="14" t="inlineStr">
         <is>
@@ -857,22 +875,22 @@
         </is>
       </c>
       <c r="B4" s="16" t="n">
-        <v>1.5</v>
+        <v>2.12</v>
       </c>
       <c r="C4" s="16" t="n">
-        <v>1.5</v>
+        <v>2.12</v>
       </c>
       <c r="D4" s="17" t="n">
-        <v>1</v>
+        <v>127</v>
       </c>
       <c r="E4" s="17" t="n">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="F4" s="17" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="G4" s="18" t="n">
-        <v>1</v>
+        <v>0.5275590551181102</v>
       </c>
       <c r="H4" s="19" t="n"/>
       <c r="I4" s="20" t="n">
@@ -901,19 +919,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="61" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="25" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="31" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="19" customWidth="1" min="13" max="13"/>
@@ -1002,60 +1020,7872 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
+          <t>NEARUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 19:55:28</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>NEARUSDT</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="n">
+        <v>4.6655</v>
+      </c>
+      <c r="G3" s="21" t="n">
+        <v>4.6605</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>PROFIT PROTECT (giveback)</t>
+        </is>
+      </c>
+      <c r="K3" s="13" t="n">
+        <v>999.21</v>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>🛡️ YES</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>FETUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 19:58:07</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>FETUSDT</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="n">
+        <v>0.21175</v>
+      </c>
+      <c r="G4" s="21" t="n">
+        <v>0.21155</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>PROFIT PROTECT (giveback)</t>
+        </is>
+      </c>
+      <c r="K4" s="13" t="n">
+        <v>999.49</v>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>🛡️ YES</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
           <t>AVAXUSDT_17915</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-10 12:00:00</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 19:58:41</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>AVAXUSDT</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>🔴 SHORT</t>
-        </is>
-      </c>
-      <c r="E3" s="10" t="inlineStr">
-        <is>
-          <t>3x</t>
-        </is>
-      </c>
-      <c r="F3" s="21" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="G3" s="21" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I3" s="10" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="n">
+        <v>10.1305</v>
+      </c>
+      <c r="G5" s="21" t="n">
+        <v>10.1255</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
         <is>
           <t>🟢 WIN</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>TP1</t>
-        </is>
-      </c>
-      <c r="K3" s="13" t="n">
-        <v>1001.5</v>
-      </c>
-      <c r="L3" s="10" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="M3" s="10" t="n">
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.59)</t>
+        </is>
+      </c>
+      <c r="K5" s="13" t="n">
+        <v>999.54</v>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>BNBUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 19:58:44</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>BNBUSDT</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="n">
+        <v>737.515</v>
+      </c>
+      <c r="G6" s="21" t="n">
+        <v>737.355</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.79)</t>
+        </is>
+      </c>
+      <c r="K6" s="13" t="n">
+        <v>999.45</v>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>RENDERUSDT_179</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 19:59:06</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>RENDERUSDT</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="n">
+        <v>1.8455</v>
+      </c>
+      <c r="G7" s="21" t="n">
+        <v>1.8415</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.75)</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="n">
+        <v>1000.19</v>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>INJUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 19:59:10</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>INJUSDT</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="n">
+        <v>6.845499999999999</v>
+      </c>
+      <c r="G8" s="21" t="n">
+        <v>6.8395</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.41)</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="n">
+        <v>999.9299999999999</v>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M8" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>TIAUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 19:59:14</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>TIAUSDT</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="n">
+        <v>0.46445</v>
+      </c>
+      <c r="G9" s="21" t="n">
+        <v>0.46455</v>
+      </c>
+      <c r="H9" s="22" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.60)</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="n">
+        <v>999.77</v>
+      </c>
+      <c r="L9" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M9" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>PAXGUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 19:59:22</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>PAXGUSDT</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>🟢 LONG</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="n">
+        <v>4190.135</v>
+      </c>
+      <c r="G10" s="21" t="n">
+        <v>4190.445</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (-0.86)</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>999.65</v>
+      </c>
+      <c r="L10" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M10" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>XRPUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 19:59:27</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>XRPUSDT</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="n">
+        <v>1.38145</v>
+      </c>
+      <c r="G11" s="21" t="n">
+        <v>1.38315</v>
+      </c>
+      <c r="H11" s="22" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.93)</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="n">
+        <v>999.23</v>
+      </c>
+      <c r="L11" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M11" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>INJUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 19:59:31</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>INJUSDT</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="n">
+        <v>6.8445</v>
+      </c>
+      <c r="G12" s="21" t="n">
+        <v>6.8415</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.92)</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>999.27</v>
+      </c>
+      <c r="L12" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M12" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>PAXGUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 19:59:40</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>PAXGUSDT</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>🟢 LONG</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="n">
+        <v>4190.575</v>
+      </c>
+      <c r="G13" s="21" t="n">
+        <v>4190.445</v>
+      </c>
+      <c r="H13" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (-0.36)</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>998.89</v>
+      </c>
+      <c r="L13" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M13" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="N3" s="10" t="inlineStr">
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>NEARUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 19:59:45</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>NEARUSDT</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="n">
+        <v>4.6585</v>
+      </c>
+      <c r="G14" s="21" t="n">
+        <v>4.6485</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.80)</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="n">
+        <v>998.51</v>
+      </c>
+      <c r="L14" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M14" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N14" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>NEARUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 19:59:49</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>NEARUSDT</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="n">
+        <v>4.657500000000001</v>
+      </c>
+      <c r="G15" s="21" t="n">
+        <v>4.6495</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.85)</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>998.33</v>
+      </c>
+      <c r="L15" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M15" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>ADAUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:00:09</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>ADAUSDT</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="n">
+        <v>0.23555</v>
+      </c>
+      <c r="G16" s="21" t="n">
+        <v>0.23565</v>
+      </c>
+      <c r="H16" s="22" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.54)</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="n">
+        <v>997.26</v>
+      </c>
+      <c r="L16" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M16" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>RENDERUSDT_179</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:00:10</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>RENDERUSDT</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="n">
+        <v>1.8455</v>
+      </c>
+      <c r="G17" s="21" t="n">
+        <v>1.8425</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>PROFIT PROTECT (giveback)</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>996.89</v>
+      </c>
+      <c r="L17" s="10" t="inlineStr">
+        <is>
+          <t>🛡️ YES</t>
+        </is>
+      </c>
+      <c r="M17" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N17" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>DOTUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:00:44</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>DOTUSDT</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>🟢 LONG</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="n">
+        <v>1.20405</v>
+      </c>
+      <c r="G18" s="21" t="n">
+        <v>1.20525</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (-0.88)</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="n">
+        <v>993.08</v>
+      </c>
+      <c r="L18" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M18" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="N18" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>WIFUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:01:14</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>WIFUSDT</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="n">
+        <v>0.20945</v>
+      </c>
+      <c r="G19" s="21" t="n">
+        <v>0.20975</v>
+      </c>
+      <c r="H19" s="22" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.60)</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>993.76</v>
+      </c>
+      <c r="L19" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M19" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N19" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>FETUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:01:31</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>FETUSDT</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="n">
+        <v>0.21135</v>
+      </c>
+      <c r="G20" s="21" t="n">
+        <v>0.21225</v>
+      </c>
+      <c r="H20" s="22" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.81)</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="n">
+        <v>991.8200000000001</v>
+      </c>
+      <c r="L20" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M20" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="N20" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>AVAXUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:01:34</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>AVAXUSDT</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="n">
+        <v>10.1245</v>
+      </c>
+      <c r="G21" s="21" t="n">
+        <v>10.1495</v>
+      </c>
+      <c r="H21" s="22" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.66)</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="n">
+        <v>991.1799999999999</v>
+      </c>
+      <c r="L21" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M21" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N21" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>ADAUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:02:10</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>ADAUSDT</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="n">
+        <v>0.23565</v>
+      </c>
+      <c r="G22" s="21" t="n">
+        <v>0.23635</v>
+      </c>
+      <c r="H22" s="22" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.54)</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="n">
+        <v>989.49</v>
+      </c>
+      <c r="L22" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M22" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N22" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>RENDERUSDT_179</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:04:30</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>RENDERUSDT</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="n">
+        <v>1.8475</v>
+      </c>
+      <c r="G23" s="21" t="n">
+        <v>1.8455</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>PROFIT PROTECT (giveback)</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="n">
+        <v>999.92</v>
+      </c>
+      <c r="L23" s="10" t="inlineStr">
+        <is>
+          <t>🛡️ YES</t>
+        </is>
+      </c>
+      <c r="M23" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N23" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>ETHUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:04:39</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>ETHUSDT</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="n">
+        <v>2478.685</v>
+      </c>
+      <c r="G24" s="21" t="n">
+        <v>2475.335</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.54)</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="n">
+        <v>999.9299999999999</v>
+      </c>
+      <c r="L24" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M24" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N24" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>AVAXUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:04:41</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>AVAXUSDT</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="n">
+        <v>10.1645</v>
+      </c>
+      <c r="G25" s="21" t="n">
+        <v>10.1465</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.50)</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="n">
+        <v>999.87</v>
+      </c>
+      <c r="L25" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M25" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N25" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>ADAUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:04:52</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>ADAUSDT</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="n">
+        <v>0.23655</v>
+      </c>
+      <c r="G26" s="21" t="n">
+        <v>0.23635</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.42)</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="n">
+        <v>999.36</v>
+      </c>
+      <c r="L26" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M26" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="N26" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>SOLUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:05:07</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>SOLUSDT</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="n">
+        <v>108.725</v>
+      </c>
+      <c r="G27" s="21" t="n">
+        <v>108.635</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.41)</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="n">
+        <v>998.8099999999999</v>
+      </c>
+      <c r="L27" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M27" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N27" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>APTUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:05:15</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>APTUSDT</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>🟢 LONG</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="n">
+        <v>0.79735</v>
+      </c>
+      <c r="G28" s="21" t="n">
+        <v>0.79665</v>
+      </c>
+      <c r="H28" s="22" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (-0.96)</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="n">
+        <v>998.89</v>
+      </c>
+      <c r="L28" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M28" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N28" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>ARBUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:05:16</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>ARBUSDT</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>🟢 LONG</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="n">
+        <v>0.179145</v>
+      </c>
+      <c r="G29" s="21" t="n">
+        <v>0.178905</v>
+      </c>
+      <c r="H29" s="22" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (-0.95)</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="n">
+        <v>998.85</v>
+      </c>
+      <c r="L29" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M29" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N29" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>TIAUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:05:20</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>TIAUSDT</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="n">
+        <v>0.46695</v>
+      </c>
+      <c r="G30" s="21" t="n">
+        <v>0.46695</v>
+      </c>
+      <c r="H30" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.52)</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="n">
+        <v>998.6900000000001</v>
+      </c>
+      <c r="L30" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M30" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="N30" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>LDOUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:05:22</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>LDOUSDT</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="n">
+        <v>0.41405</v>
+      </c>
+      <c r="G31" s="21" t="n">
+        <v>0.41305</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.82)</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="n">
+        <v>998.6799999999999</v>
+      </c>
+      <c r="L31" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M31" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="N31" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>DOTUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:05:23</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>DOTUSDT</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>🟢 LONG</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F32" s="21" t="n">
+        <v>1.21205</v>
+      </c>
+      <c r="G32" s="21" t="n">
+        <v>1.20755</v>
+      </c>
+      <c r="H32" s="22" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (-0.38)</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="n">
+        <v>998.61</v>
+      </c>
+      <c r="L32" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M32" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="N32" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>SEIUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:05:36</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>SEIUSDT</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="n">
+        <v>0.065165</v>
+      </c>
+      <c r="G33" s="21" t="n">
+        <v>0.06501499999999999</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.36)</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="n">
+        <v>998.08</v>
+      </c>
+      <c r="L33" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M33" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="N33" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>TIAUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:05:40</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>TIAUSDT</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="n">
+        <v>0.46695</v>
+      </c>
+      <c r="G34" s="21" t="n">
+        <v>0.4665</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.83)</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="n">
+        <v>998.29</v>
+      </c>
+      <c r="L34" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M34" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="N34" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>AAVEUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:05:54</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>AAVEUSDT</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F35" s="21" t="n">
+        <v>167.265</v>
+      </c>
+      <c r="G35" s="21" t="n">
+        <v>167.085</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>PROFIT PROTECT (giveback)</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="n">
+        <v>996.37</v>
+      </c>
+      <c r="L35" s="10" t="inlineStr">
+        <is>
+          <t>🛡️ YES</t>
+        </is>
+      </c>
+      <c r="M35" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N35" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>SEIUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:05:54</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>SEIUSDT</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F36" s="21" t="n">
+        <v>0.06512499999999999</v>
+      </c>
+      <c r="G36" s="21" t="n">
+        <v>0.065055</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>PROFIT PROTECT (giveback)</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="n">
+        <v>996.27</v>
+      </c>
+      <c r="L36" s="10" t="inlineStr">
+        <is>
+          <t>🛡️ YES</t>
+        </is>
+      </c>
+      <c r="M36" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N36" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>ETHUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:05:57</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>ETHUSDT</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F37" s="21" t="n">
+        <v>2477.275</v>
+      </c>
+      <c r="G37" s="21" t="n">
+        <v>2475.935</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.72)</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="n">
+        <v>996.24</v>
+      </c>
+      <c r="L37" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M37" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N37" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>APTUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:06:41</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>APTUSDT</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>🟢 LONG</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F38" s="21" t="n">
+        <v>0.7968500000000001</v>
+      </c>
+      <c r="G38" s="21" t="n">
+        <v>0.79705</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (-0.54)</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="n">
+        <v>996.38</v>
+      </c>
+      <c r="L38" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M38" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N38" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>APTUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:07:13</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>APTUSDT</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>🟢 LONG</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F39" s="21" t="n">
+        <v>0.79675</v>
+      </c>
+      <c r="G39" s="21" t="n">
+        <v>0.79595</v>
+      </c>
+      <c r="H39" s="22" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (-0.68)</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="n">
+        <v>997.5700000000001</v>
+      </c>
+      <c r="L39" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M39" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N39" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>TIAUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:07:15</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>TIAUSDT</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F40" s="21" t="n">
+        <v>0.46665</v>
+      </c>
+      <c r="G40" s="21" t="n">
+        <v>0.46625</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>PROFIT PROTECT (giveback)</t>
+        </is>
+      </c>
+      <c r="K40" s="13" t="n">
+        <v>997.54</v>
+      </c>
+      <c r="L40" s="10" t="inlineStr">
+        <is>
+          <t>🛡️ YES</t>
+        </is>
+      </c>
+      <c r="M40" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="N40" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>AVAXUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:07:32</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>AVAXUSDT</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F41" s="21" t="n">
+        <v>10.1455</v>
+      </c>
+      <c r="G41" s="21" t="n">
+        <v>10.1455</v>
+      </c>
+      <c r="H41" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.98)</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="n">
+        <v>996.48</v>
+      </c>
+      <c r="L41" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M41" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N41" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>SOLUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:07:40</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>SOLUSDT</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F42" s="21" t="n">
+        <v>108.585</v>
+      </c>
+      <c r="G42" s="21" t="n">
+        <v>108.665</v>
+      </c>
+      <c r="H42" s="22" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.85)</t>
+        </is>
+      </c>
+      <c r="K42" s="13" t="n">
+        <v>996.3</v>
+      </c>
+      <c r="L42" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M42" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N42" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>AAVEUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:07:44</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>AAVEUSDT</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F43" s="21" t="n">
+        <v>166.895</v>
+      </c>
+      <c r="G43" s="21" t="n">
+        <v>167.025</v>
+      </c>
+      <c r="H43" s="22" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.50)</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="n">
+        <v>995.89</v>
+      </c>
+      <c r="L43" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M43" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N43" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>LDOUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:07:46</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>LDOUSDT</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F44" s="21" t="n">
+        <v>0.41295</v>
+      </c>
+      <c r="G44" s="21" t="n">
+        <v>0.41295</v>
+      </c>
+      <c r="H44" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.94)</t>
+        </is>
+      </c>
+      <c r="K44" s="13" t="n">
+        <v>995.84</v>
+      </c>
+      <c r="L44" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M44" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="N44" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>RENDERUSDT_179</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:07:49</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>RENDERUSDT</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F45" s="21" t="n">
+        <v>1.8445</v>
+      </c>
+      <c r="G45" s="21" t="n">
+        <v>1.8455</v>
+      </c>
+      <c r="H45" s="22" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.83)</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="n">
+        <v>995.78</v>
+      </c>
+      <c r="L45" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M45" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N45" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>ARBUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:07:58</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>ARBUSDT</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>🟢 LONG</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F46" s="21" t="n">
+        <v>0.179035</v>
+      </c>
+      <c r="G46" s="21" t="n">
+        <v>0.179245</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="I46" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (-0.77)</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="n">
+        <v>995.9400000000001</v>
+      </c>
+      <c r="L46" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M46" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N46" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>APTUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:08:23</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>APTUSDT</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>🟢 LONG</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F47" s="21" t="n">
+        <v>0.7958499999999999</v>
+      </c>
+      <c r="G47" s="21" t="n">
+        <v>0.79675</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>PROFIT PROTECT (giveback)</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="n">
+        <v>994.75</v>
+      </c>
+      <c r="L47" s="10" t="inlineStr">
+        <is>
+          <t>🛡️ YES</t>
+        </is>
+      </c>
+      <c r="M47" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N47" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>ARBUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:09:14</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>ARBUSDT</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>🟢 LONG</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F48" s="21" t="n">
+        <v>0.179195</v>
+      </c>
+      <c r="G48" s="21" t="n">
+        <v>0.179355</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>PROFIT PROTECT (giveback)</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="n">
+        <v>999.45</v>
+      </c>
+      <c r="L48" s="10" t="inlineStr">
+        <is>
+          <t>🛡️ YES</t>
+        </is>
+      </c>
+      <c r="M48" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N48" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>SOLUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:10:56</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>SOLUSDT</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F49" s="21" t="n">
+        <v>108.715</v>
+      </c>
+      <c r="G49" s="21" t="n">
+        <v>108.775</v>
+      </c>
+      <c r="H49" s="22" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.77)</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="n">
+        <v>998.77</v>
+      </c>
+      <c r="L49" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M49" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N49" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>LINKUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:10:58</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>LINKUSDT</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F50" s="21" t="n">
+        <v>12.7585</v>
+      </c>
+      <c r="G50" s="21" t="n">
+        <v>12.7645</v>
+      </c>
+      <c r="H50" s="22" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.88)</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="n">
+        <v>998.55</v>
+      </c>
+      <c r="L50" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M50" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="N50" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>XRPUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:11:05</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>XRPUSDT</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F51" s="21" t="n">
+        <v>1.38645</v>
+      </c>
+      <c r="G51" s="21" t="n">
+        <v>1.38655</v>
+      </c>
+      <c r="H51" s="22" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I51" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.62)</t>
+        </is>
+      </c>
+      <c r="K51" s="13" t="n">
+        <v>998.64</v>
+      </c>
+      <c r="L51" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M51" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N51" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>AVAXUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:11:29</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>AVAXUSDT</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F52" s="21" t="n">
+        <v>10.1485</v>
+      </c>
+      <c r="G52" s="21" t="n">
+        <v>10.1585</v>
+      </c>
+      <c r="H52" s="22" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="I52" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.74)</t>
+        </is>
+      </c>
+      <c r="K52" s="13" t="n">
+        <v>997.47</v>
+      </c>
+      <c r="L52" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M52" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N52" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>AAVEUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:11:33</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>AAVEUSDT</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F53" s="21" t="n">
+        <v>167.085</v>
+      </c>
+      <c r="G53" s="21" t="n">
+        <v>167.215</v>
+      </c>
+      <c r="H53" s="22" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="I53" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.46)</t>
+        </is>
+      </c>
+      <c r="K53" s="13" t="n">
+        <v>997.35</v>
+      </c>
+      <c r="L53" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M53" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="N53" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>FILUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:12:45</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>FILUSDT</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F54" s="21" t="n">
+        <v>1.07175</v>
+      </c>
+      <c r="G54" s="21" t="n">
+        <v>1.07415</v>
+      </c>
+      <c r="H54" s="22" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="I54" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.93)</t>
+        </is>
+      </c>
+      <c r="K54" s="13" t="n">
+        <v>998.65</v>
+      </c>
+      <c r="L54" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M54" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="N54" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>LINKUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:12:49</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>LINKUSDT</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F55" s="21" t="n">
+        <v>12.7685</v>
+      </c>
+      <c r="G55" s="21" t="n">
+        <v>12.7765</v>
+      </c>
+      <c r="H55" s="22" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="I55" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.76)</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="n">
+        <v>998.5</v>
+      </c>
+      <c r="L55" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M55" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N55" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>NEARUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:12:57</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>NEARUSDT</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E56" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F56" s="21" t="n">
+        <v>4.6605</v>
+      </c>
+      <c r="G56" s="21" t="n">
+        <v>4.669499999999999</v>
+      </c>
+      <c r="H56" s="22" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="I56" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.51)</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="n">
+        <v>998.41</v>
+      </c>
+      <c r="L56" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M56" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N56" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>AVAXUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:13:12</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>AVAXUSDT</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E57" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F57" s="21" t="n">
+        <v>10.1545</v>
+      </c>
+      <c r="G57" s="21" t="n">
+        <v>10.1715</v>
+      </c>
+      <c r="H57" s="22" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="I57" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.40)</t>
+        </is>
+      </c>
+      <c r="K57" s="13" t="n">
+        <v>998.47</v>
+      </c>
+      <c r="L57" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M57" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="N57" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>APTUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:13:28</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>APTUSDT</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>🟢 LONG</t>
+        </is>
+      </c>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F58" s="21" t="n">
+        <v>0.79695</v>
+      </c>
+      <c r="G58" s="21" t="n">
+        <v>0.80605</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (-0.98)</t>
+        </is>
+      </c>
+      <c r="K58" s="13" t="n">
+        <v>997.9</v>
+      </c>
+      <c r="L58" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M58" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N58" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>DOTUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:13:33</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>DOTUSDT</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>🟢 LONG</t>
+        </is>
+      </c>
+      <c r="E59" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F59" s="21" t="n">
+        <v>1.20925</v>
+      </c>
+      <c r="G59" s="21" t="n">
+        <v>1.21475</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="I59" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (-0.58)</t>
+        </is>
+      </c>
+      <c r="K59" s="13" t="n">
+        <v>997.91</v>
+      </c>
+      <c r="L59" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M59" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="N59" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>APTUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:13:37</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>APTUSDT</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>🟢 LONG</t>
+        </is>
+      </c>
+      <c r="E60" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F60" s="21" t="n">
+        <v>0.80045</v>
+      </c>
+      <c r="G60" s="21" t="n">
+        <v>0.80735</v>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I60" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (-0.40)</t>
+        </is>
+      </c>
+      <c r="K60" s="13" t="n">
+        <v>997.8200000000001</v>
+      </c>
+      <c r="L60" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M60" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="N60" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>NEARUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:13:41</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>NEARUSDT</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E61" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F61" s="21" t="n">
+        <v>4.6675</v>
+      </c>
+      <c r="G61" s="21" t="n">
+        <v>4.673500000000001</v>
+      </c>
+      <c r="H61" s="22" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="I61" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.78)</t>
+        </is>
+      </c>
+      <c r="K61" s="13" t="n">
+        <v>997.6799999999999</v>
+      </c>
+      <c r="L61" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M61" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N61" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>AVAXUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:13:58</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>AVAXUSDT</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F62" s="21" t="n">
+        <v>10.1485</v>
+      </c>
+      <c r="G62" s="21" t="n">
+        <v>10.1725</v>
+      </c>
+      <c r="H62" s="22" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="I62" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.80)</t>
+        </is>
+      </c>
+      <c r="K62" s="13" t="n">
+        <v>997.4400000000001</v>
+      </c>
+      <c r="L62" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M62" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N62" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>LDOUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:14:27</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>LDOUSDT</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E63" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F63" s="21" t="n">
+        <v>0.4133</v>
+      </c>
+      <c r="G63" s="21" t="n">
+        <v>0.41505</v>
+      </c>
+      <c r="H63" s="22" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="I63" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.98)</t>
+        </is>
+      </c>
+      <c r="K63" s="13" t="n">
+        <v>997.14</v>
+      </c>
+      <c r="L63" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M63" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="N63" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>ADAUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:14:53</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>ADAUSDT</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F64" s="21" t="n">
+        <v>0.23635</v>
+      </c>
+      <c r="G64" s="21" t="n">
+        <v>0.23695</v>
+      </c>
+      <c r="H64" s="22" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="I64" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.74)</t>
+        </is>
+      </c>
+      <c r="K64" s="13" t="n">
+        <v>996.97</v>
+      </c>
+      <c r="L64" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M64" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="N64" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>DOTUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:15:03</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>DOTUSDT</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>🟢 LONG</t>
+        </is>
+      </c>
+      <c r="E65" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F65" s="21" t="n">
+        <v>1.21445</v>
+      </c>
+      <c r="G65" s="21" t="n">
+        <v>1.21795</v>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I65" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>PROFIT PROTECT (giveback)</t>
+        </is>
+      </c>
+      <c r="K65" s="13" t="n">
+        <v>997.89</v>
+      </c>
+      <c r="L65" s="10" t="inlineStr">
+        <is>
+          <t>🛡️ YES</t>
+        </is>
+      </c>
+      <c r="M65" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="N65" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>ADAUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:15:15</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>ADAUSDT</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F66" s="21" t="n">
+        <v>0.23645</v>
+      </c>
+      <c r="G66" s="21" t="n">
+        <v>0.23685</v>
+      </c>
+      <c r="H66" s="22" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="I66" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.75)</t>
+        </is>
+      </c>
+      <c r="K66" s="13" t="n">
+        <v>996.78</v>
+      </c>
+      <c r="L66" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M66" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="N66" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>LINKUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:15:20</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>LINKUSDT</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E67" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F67" s="21" t="n">
+        <v>12.7735</v>
+      </c>
+      <c r="G67" s="21" t="n">
+        <v>12.7785</v>
+      </c>
+      <c r="H67" s="22" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="I67" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.78)</t>
+        </is>
+      </c>
+      <c r="K67" s="13" t="n">
+        <v>996.67</v>
+      </c>
+      <c r="L67" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M67" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N67" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>APTUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:15:49</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>APTUSDT</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>🟢 LONG</t>
+        </is>
+      </c>
+      <c r="E68" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F68" s="21" t="n">
+        <v>0.80705</v>
+      </c>
+      <c r="G68" s="21" t="n">
+        <v>0.80845</v>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I68" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (-0.98)</t>
+        </is>
+      </c>
+      <c r="K68" s="13" t="n">
+        <v>995.97</v>
+      </c>
+      <c r="L68" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M68" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N68" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>LDOUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:15:58</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>LDOUSDT</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E69" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F69" s="21" t="n">
+        <v>0.41475</v>
+      </c>
+      <c r="G69" s="21" t="n">
+        <v>0.41535</v>
+      </c>
+      <c r="H69" s="22" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="I69" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.48)</t>
+        </is>
+      </c>
+      <c r="K69" s="13" t="n">
+        <v>994.98</v>
+      </c>
+      <c r="L69" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M69" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="N69" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>FETUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B70" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:16:06</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>FETUSDT</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F70" s="21" t="n">
+        <v>0.21285</v>
+      </c>
+      <c r="G70" s="21" t="n">
+        <v>0.21325</v>
+      </c>
+      <c r="H70" s="22" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="I70" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.73)</t>
+        </is>
+      </c>
+      <c r="K70" s="13" t="n">
+        <v>995.45</v>
+      </c>
+      <c r="L70" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M70" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N70" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>ARBUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B71" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:16:23</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>ARBUSDT</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>🟢 LONG</t>
+        </is>
+      </c>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F71" s="21" t="n">
+        <v>0.180465</v>
+      </c>
+      <c r="G71" s="21" t="n">
+        <v>0.180565</v>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I71" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (-0.99)</t>
+        </is>
+      </c>
+      <c r="K71" s="13" t="n">
+        <v>995.58</v>
+      </c>
+      <c r="L71" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M71" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N71" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>NEARUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:16:58</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>NEARUSDT</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F72" s="21" t="n">
+        <v>4.669499999999999</v>
+      </c>
+      <c r="G72" s="21" t="n">
+        <v>4.6765</v>
+      </c>
+      <c r="H72" s="22" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="I72" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.65)</t>
+        </is>
+      </c>
+      <c r="K72" s="13" t="n">
+        <v>994.46</v>
+      </c>
+      <c r="L72" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M72" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N72" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>LINKUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B73" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:17:12</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>LINKUSDT</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E73" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F73" s="21" t="n">
+        <v>12.7735</v>
+      </c>
+      <c r="G73" s="21" t="n">
+        <v>12.7935</v>
+      </c>
+      <c r="H73" s="22" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="I73" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.62)</t>
+        </is>
+      </c>
+      <c r="K73" s="13" t="n">
+        <v>994.13</v>
+      </c>
+      <c r="L73" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M73" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N73" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
+          <t>AVAXUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B74" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:17:18</t>
+        </is>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>AVAXUSDT</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E74" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F74" s="21" t="n">
+        <v>10.1725</v>
+      </c>
+      <c r="G74" s="21" t="n">
+        <v>10.1905</v>
+      </c>
+      <c r="H74" s="22" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="I74" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.84)</t>
+        </is>
+      </c>
+      <c r="K74" s="13" t="n">
+        <v>993.79</v>
+      </c>
+      <c r="L74" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M74" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="N74" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>AVAXUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B75" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:17:45</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>AVAXUSDT</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F75" s="21" t="n">
+        <v>10.1795</v>
+      </c>
+      <c r="G75" s="21" t="n">
+        <v>10.1775</v>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.36)</t>
+        </is>
+      </c>
+      <c r="K75" s="13" t="n">
+        <v>994.73</v>
+      </c>
+      <c r="L75" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M75" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N75" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>ARBUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B76" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:18:46</t>
+        </is>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>ARBUSDT</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>🟢 LONG</t>
+        </is>
+      </c>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F76" s="21" t="n">
+        <v>0.180305</v>
+      </c>
+      <c r="G76" s="21" t="n">
+        <v>0.180265</v>
+      </c>
+      <c r="H76" s="22" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="I76" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>TRAILING STOP TRIGGERED</t>
+        </is>
+      </c>
+      <c r="K76" s="13" t="n">
+        <v>993.75</v>
+      </c>
+      <c r="L76" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M76" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="N76" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>LDOUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B77" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:18:50</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t>LDOUSDT</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E77" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F77" s="21" t="n">
+        <v>0.41555</v>
+      </c>
+      <c r="G77" s="21" t="n">
+        <v>0.41485</v>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I77" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.59)</t>
+        </is>
+      </c>
+      <c r="K77" s="13" t="n">
+        <v>993.52</v>
+      </c>
+      <c r="L77" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M77" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="N77" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>SOLUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B78" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:18:54</t>
+        </is>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t>SOLUSDT</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E78" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F78" s="21" t="n">
+        <v>108.985</v>
+      </c>
+      <c r="G78" s="21" t="n">
+        <v>108.965</v>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.47)</t>
+        </is>
+      </c>
+      <c r="K78" s="13" t="n">
+        <v>993.34</v>
+      </c>
+      <c r="L78" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M78" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N78" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>WIFUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B79" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:19:01</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>WIFUSDT</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E79" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F79" s="21" t="n">
+        <v>0.21065</v>
+      </c>
+      <c r="G79" s="21" t="n">
+        <v>0.21075</v>
+      </c>
+      <c r="H79" s="22" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="I79" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.93)</t>
+        </is>
+      </c>
+      <c r="K79" s="13" t="n">
+        <v>993.03</v>
+      </c>
+      <c r="L79" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M79" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N79" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>NEARUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B80" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:19:55</t>
+        </is>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>NEARUSDT</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E80" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F80" s="21" t="n">
+        <v>4.6655</v>
+      </c>
+      <c r="G80" s="21" t="n">
+        <v>4.6845</v>
+      </c>
+      <c r="H80" s="22" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="I80" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.69)</t>
+        </is>
+      </c>
+      <c r="K80" s="13" t="n">
+        <v>991.6</v>
+      </c>
+      <c r="L80" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M80" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N80" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>ARBUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:19:58</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>ARBUSDT</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>🟢 LONG</t>
+        </is>
+      </c>
+      <c r="E81" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F81" s="21" t="n">
+        <v>0.180795</v>
+      </c>
+      <c r="G81" s="21" t="n">
+        <v>0.180435</v>
+      </c>
+      <c r="H81" s="22" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="I81" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (-0.83)</t>
+        </is>
+      </c>
+      <c r="K81" s="13" t="n">
+        <v>991.5</v>
+      </c>
+      <c r="L81" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M81" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N81" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>FILUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B82" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:20:02</t>
+        </is>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>FILUSDT</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>🟢 LONG</t>
+        </is>
+      </c>
+      <c r="E82" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F82" s="21" t="n">
+        <v>1.07775</v>
+      </c>
+      <c r="G82" s="21" t="n">
+        <v>1.07805</v>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I82" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (-0.99)</t>
+        </is>
+      </c>
+      <c r="K82" s="13" t="n">
+        <v>991.52</v>
+      </c>
+      <c r="L82" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M82" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="N82" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>RENDERUSDT_179</t>
+        </is>
+      </c>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:21:44</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t>RENDERUSDT</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E83" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F83" s="21" t="n">
+        <v>1.8575</v>
+      </c>
+      <c r="G83" s="21" t="n">
+        <v>1.8555</v>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I83" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>PROFIT PROTECT (giveback)</t>
+        </is>
+      </c>
+      <c r="K83" s="13" t="n">
+        <v>998.48</v>
+      </c>
+      <c r="L83" s="10" t="inlineStr">
+        <is>
+          <t>🛡️ YES</t>
+        </is>
+      </c>
+      <c r="M83" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N83" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>ETHUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B84" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:22:30</t>
+        </is>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t>ETHUSDT</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E84" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F84" s="21" t="n">
+        <v>2479.215</v>
+      </c>
+      <c r="G84" s="21" t="n">
+        <v>2480.095</v>
+      </c>
+      <c r="H84" s="22" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="I84" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.89)</t>
+        </is>
+      </c>
+      <c r="K84" s="13" t="n">
+        <v>998.9400000000001</v>
+      </c>
+      <c r="L84" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M84" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N84" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>BTCUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:22:57</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E85" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F85" s="21" t="n">
+        <v>82392.64999999999</v>
+      </c>
+      <c r="G85" s="21" t="n">
+        <v>82413.95</v>
+      </c>
+      <c r="H85" s="22" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I85" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.52)</t>
+        </is>
+      </c>
+      <c r="K85" s="13" t="n">
+        <v>999.15</v>
+      </c>
+      <c r="L85" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M85" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N85" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>SEIUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B86" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:23:00</t>
+        </is>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>SEIUSDT</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E86" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F86" s="21" t="n">
+        <v>0.06539500000000001</v>
+      </c>
+      <c r="G86" s="21" t="n">
+        <v>0.065335</v>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="I86" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.90)</t>
+        </is>
+      </c>
+      <c r="K86" s="13" t="n">
+        <v>998.98</v>
+      </c>
+      <c r="L86" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M86" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="N86" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>UNIUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B87" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:23:01</t>
+        </is>
+      </c>
+      <c r="C87" s="10" t="inlineStr">
+        <is>
+          <t>UNIUSDT</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E87" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F87" s="21" t="n">
+        <v>7.2905</v>
+      </c>
+      <c r="G87" s="21" t="n">
+        <v>7.2855</v>
+      </c>
+      <c r="H87" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I87" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.95)</t>
+        </is>
+      </c>
+      <c r="K87" s="13" t="n">
+        <v>998.88</v>
+      </c>
+      <c r="L87" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M87" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N87" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>AVAXUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B88" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:23:14</t>
+        </is>
+      </c>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>AVAXUSDT</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E88" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F88" s="21" t="n">
+        <v>10.1845</v>
+      </c>
+      <c r="G88" s="21" t="n">
+        <v>10.1945</v>
+      </c>
+      <c r="H88" s="22" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="I88" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.43)</t>
+        </is>
+      </c>
+      <c r="K88" s="13" t="n">
+        <v>998.01</v>
+      </c>
+      <c r="L88" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M88" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N88" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>OPUSDT_1791577</t>
+        </is>
+      </c>
+      <c r="B89" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:23:44</t>
+        </is>
+      </c>
+      <c r="C89" s="10" t="inlineStr">
+        <is>
+          <t>OPUSDT</t>
+        </is>
+      </c>
+      <c r="D89" s="10" t="inlineStr">
+        <is>
+          <t>🟢 LONG</t>
+        </is>
+      </c>
+      <c r="E89" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F89" s="21" t="n">
+        <v>0.127295</v>
+      </c>
+      <c r="G89" s="21" t="n">
+        <v>0.127065</v>
+      </c>
+      <c r="H89" s="22" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="I89" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (-0.65)</t>
+        </is>
+      </c>
+      <c r="K89" s="13" t="n">
+        <v>999.5599999999999</v>
+      </c>
+      <c r="L89" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M89" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N89" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>NEARUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:24:09</t>
+        </is>
+      </c>
+      <c r="C90" s="10" t="inlineStr">
+        <is>
+          <t>NEARUSDT</t>
+        </is>
+      </c>
+      <c r="D90" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E90" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F90" s="21" t="n">
+        <v>4.6875</v>
+      </c>
+      <c r="G90" s="21" t="n">
+        <v>4.670500000000001</v>
+      </c>
+      <c r="H90" s="5" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="I90" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.99)</t>
+        </is>
+      </c>
+      <c r="K90" s="13" t="n">
+        <v>1000.04</v>
+      </c>
+      <c r="L90" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M90" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N90" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>RENDERUSDT_179</t>
+        </is>
+      </c>
+      <c r="B91" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:24:10</t>
+        </is>
+      </c>
+      <c r="C91" s="10" t="inlineStr">
+        <is>
+          <t>RENDERUSDT</t>
+        </is>
+      </c>
+      <c r="D91" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E91" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F91" s="21" t="n">
+        <v>1.8545</v>
+      </c>
+      <c r="G91" s="21" t="n">
+        <v>1.8525</v>
+      </c>
+      <c r="H91" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I91" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.65)</t>
+        </is>
+      </c>
+      <c r="K91" s="13" t="n">
+        <v>999.9400000000001</v>
+      </c>
+      <c r="L91" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M91" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N91" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="10" t="inlineStr">
+        <is>
+          <t>TIAUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B92" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:24:40</t>
+        </is>
+      </c>
+      <c r="C92" s="10" t="inlineStr">
+        <is>
+          <t>TIAUSDT</t>
+        </is>
+      </c>
+      <c r="D92" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E92" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F92" s="21" t="n">
+        <v>0.46845</v>
+      </c>
+      <c r="G92" s="21" t="n">
+        <v>0.46795</v>
+      </c>
+      <c r="H92" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I92" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>PROFIT PROTECT (giveback)</t>
+        </is>
+      </c>
+      <c r="K92" s="13" t="n">
+        <v>999.42</v>
+      </c>
+      <c r="L92" s="10" t="inlineStr">
+        <is>
+          <t>🛡️ YES</t>
+        </is>
+      </c>
+      <c r="M92" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="N92" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="10" t="inlineStr">
+        <is>
+          <t>BTCUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B93" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:25:01</t>
+        </is>
+      </c>
+      <c r="C93" s="10" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="D93" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E93" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F93" s="21" t="n">
+        <v>82413.95</v>
+      </c>
+      <c r="G93" s="21" t="n">
+        <v>82392.85000000001</v>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I93" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.66)</t>
+        </is>
+      </c>
+      <c r="K93" s="13" t="n">
+        <v>999.41</v>
+      </c>
+      <c r="L93" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M93" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N93" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="10" t="inlineStr">
+        <is>
+          <t>INJUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B94" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:25:10</t>
+        </is>
+      </c>
+      <c r="C94" s="10" t="inlineStr">
+        <is>
+          <t>INJUSDT</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E94" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F94" s="21" t="n">
+        <v>6.891500000000001</v>
+      </c>
+      <c r="G94" s="21" t="n">
+        <v>6.8805</v>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="I94" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.73)</t>
+        </is>
+      </c>
+      <c r="K94" s="13" t="n">
+        <v>998.38</v>
+      </c>
+      <c r="L94" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M94" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="N94" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="10" t="inlineStr">
+        <is>
+          <t>AVAXUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B95" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:25:14</t>
+        </is>
+      </c>
+      <c r="C95" s="10" t="inlineStr">
+        <is>
+          <t>AVAXUSDT</t>
+        </is>
+      </c>
+      <c r="D95" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E95" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F95" s="21" t="n">
+        <v>10.1935</v>
+      </c>
+      <c r="G95" s="21" t="n">
+        <v>10.1975</v>
+      </c>
+      <c r="H95" s="22" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="I95" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.95)</t>
+        </is>
+      </c>
+      <c r="K95" s="13" t="n">
+        <v>998.21</v>
+      </c>
+      <c r="L95" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M95" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N95" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="10" t="inlineStr">
+        <is>
+          <t>BNBUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B96" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:25:17</t>
+        </is>
+      </c>
+      <c r="C96" s="10" t="inlineStr">
+        <is>
+          <t>BNBUSDT</t>
+        </is>
+      </c>
+      <c r="D96" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E96" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F96" s="21" t="n">
+        <v>740.015</v>
+      </c>
+      <c r="G96" s="21" t="n">
+        <v>739.625</v>
+      </c>
+      <c r="H96" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I96" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.63)</t>
+        </is>
+      </c>
+      <c r="K96" s="13" t="n">
+        <v>998.11</v>
+      </c>
+      <c r="L96" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M96" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N96" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t>INJUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B97" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:25:17</t>
+        </is>
+      </c>
+      <c r="C97" s="10" t="inlineStr">
+        <is>
+          <t>INJUSDT</t>
+        </is>
+      </c>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E97" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F97" s="21" t="n">
+        <v>6.890499999999999</v>
+      </c>
+      <c r="G97" s="21" t="n">
+        <v>6.8815</v>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I97" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>PROFIT PROTECT (giveback)</t>
+        </is>
+      </c>
+      <c r="K97" s="13" t="n">
+        <v>998.01</v>
+      </c>
+      <c r="L97" s="10" t="inlineStr">
+        <is>
+          <t>🛡️ YES</t>
+        </is>
+      </c>
+      <c r="M97" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N97" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="10" t="inlineStr">
+        <is>
+          <t>INJUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B98" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:25:18</t>
+        </is>
+      </c>
+      <c r="C98" s="10" t="inlineStr">
+        <is>
+          <t>INJUSDT</t>
+        </is>
+      </c>
+      <c r="D98" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E98" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F98" s="21" t="n">
+        <v>6.887499999999999</v>
+      </c>
+      <c r="G98" s="21" t="n">
+        <v>6.8815</v>
+      </c>
+      <c r="H98" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I98" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>PROFIT PROTECT (giveback)</t>
+        </is>
+      </c>
+      <c r="K98" s="13" t="n">
+        <v>997.92</v>
+      </c>
+      <c r="L98" s="10" t="inlineStr">
+        <is>
+          <t>🛡️ YES</t>
+        </is>
+      </c>
+      <c r="M98" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N98" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="10" t="inlineStr">
+        <is>
+          <t>NEARUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B99" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:25:22</t>
+        </is>
+      </c>
+      <c r="C99" s="10" t="inlineStr">
+        <is>
+          <t>NEARUSDT</t>
+        </is>
+      </c>
+      <c r="D99" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E99" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F99" s="21" t="n">
+        <v>4.6805</v>
+      </c>
+      <c r="G99" s="21" t="n">
+        <v>4.6765</v>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I99" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.77)</t>
+        </is>
+      </c>
+      <c r="K99" s="13" t="n">
+        <v>997.86</v>
+      </c>
+      <c r="L99" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M99" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N99" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="10" t="inlineStr">
+        <is>
+          <t>PAXGUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B100" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:25:32</t>
+        </is>
+      </c>
+      <c r="C100" s="10" t="inlineStr">
+        <is>
+          <t>PAXGUSDT</t>
+        </is>
+      </c>
+      <c r="D100" s="10" t="inlineStr">
+        <is>
+          <t>🟢 LONG</t>
+        </is>
+      </c>
+      <c r="E100" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F100" s="21" t="n">
+        <v>4191.475</v>
+      </c>
+      <c r="G100" s="21" t="n">
+        <v>4191.955</v>
+      </c>
+      <c r="H100" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I100" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (-0.92)</t>
+        </is>
+      </c>
+      <c r="K100" s="13" t="n">
+        <v>997.23</v>
+      </c>
+      <c r="L100" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M100" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N100" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="10" t="inlineStr">
+        <is>
+          <t>PAXGUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B101" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:25:35</t>
+        </is>
+      </c>
+      <c r="C101" s="10" t="inlineStr">
+        <is>
+          <t>PAXGUSDT</t>
+        </is>
+      </c>
+      <c r="D101" s="10" t="inlineStr">
+        <is>
+          <t>🟢 LONG</t>
+        </is>
+      </c>
+      <c r="E101" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F101" s="21" t="n">
+        <v>4191.525</v>
+      </c>
+      <c r="G101" s="21" t="n">
+        <v>4191.955</v>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I101" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (-0.95)</t>
+        </is>
+      </c>
+      <c r="K101" s="13" t="n">
+        <v>997.15</v>
+      </c>
+      <c r="L101" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M101" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N101" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="10" t="inlineStr">
+        <is>
+          <t>PAXGUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B102" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:25:39</t>
+        </is>
+      </c>
+      <c r="C102" s="10" t="inlineStr">
+        <is>
+          <t>PAXGUSDT</t>
+        </is>
+      </c>
+      <c r="D102" s="10" t="inlineStr">
+        <is>
+          <t>🟢 LONG</t>
+        </is>
+      </c>
+      <c r="E102" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F102" s="21" t="n">
+        <v>4192.445</v>
+      </c>
+      <c r="G102" s="21" t="n">
+        <v>4191.955</v>
+      </c>
+      <c r="H102" s="22" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I102" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (-0.95)</t>
+        </is>
+      </c>
+      <c r="K102" s="13" t="n">
+        <v>997.27</v>
+      </c>
+      <c r="L102" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M102" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N102" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="10" t="inlineStr">
+        <is>
+          <t>BTCUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B103" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:25:58</t>
+        </is>
+      </c>
+      <c r="C103" s="10" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="D103" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E103" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F103" s="21" t="n">
+        <v>82400.05</v>
+      </c>
+      <c r="G103" s="21" t="n">
+        <v>82401.05</v>
+      </c>
+      <c r="H103" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.61)</t>
+        </is>
+      </c>
+      <c r="K103" s="13" t="n">
+        <v>996.85</v>
+      </c>
+      <c r="L103" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M103" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N103" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="10" t="inlineStr">
+        <is>
+          <t>SEIUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B104" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:26:39</t>
+        </is>
+      </c>
+      <c r="C104" s="10" t="inlineStr">
+        <is>
+          <t>SEIUSDT</t>
+        </is>
+      </c>
+      <c r="D104" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E104" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F104" s="21" t="n">
+        <v>0.065245</v>
+      </c>
+      <c r="G104" s="21" t="n">
+        <v>0.065215</v>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I104" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.82)</t>
+        </is>
+      </c>
+      <c r="K104" s="13" t="n">
+        <v>997.61</v>
+      </c>
+      <c r="L104" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M104" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N104" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="10" t="inlineStr">
+        <is>
+          <t>BNBUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B105" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:26:46</t>
+        </is>
+      </c>
+      <c r="C105" s="10" t="inlineStr">
+        <is>
+          <t>BNBUSDT</t>
+        </is>
+      </c>
+      <c r="D105" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E105" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F105" s="21" t="n">
+        <v>739.4349999999999</v>
+      </c>
+      <c r="G105" s="21" t="n">
+        <v>739.365</v>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I105" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.36)</t>
+        </is>
+      </c>
+      <c r="K105" s="13" t="n">
+        <v>997.4400000000001</v>
+      </c>
+      <c r="L105" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M105" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N105" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="10" t="inlineStr">
+        <is>
+          <t>ETHUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B106" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:27:52</t>
+        </is>
+      </c>
+      <c r="C106" s="10" t="inlineStr">
+        <is>
+          <t>ETHUSDT</t>
+        </is>
+      </c>
+      <c r="D106" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E106" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F106" s="21" t="n">
+        <v>2479.725</v>
+      </c>
+      <c r="G106" s="21" t="n">
+        <v>2478.575</v>
+      </c>
+      <c r="H106" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I106" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.45)</t>
+        </is>
+      </c>
+      <c r="K106" s="13" t="n">
+        <v>997.6</v>
+      </c>
+      <c r="L106" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M106" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N106" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="10" t="inlineStr">
+        <is>
+          <t>SOLUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B107" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:28:11</t>
+        </is>
+      </c>
+      <c r="C107" s="10" t="inlineStr">
+        <is>
+          <t>SOLUSDT</t>
+        </is>
+      </c>
+      <c r="D107" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E107" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F107" s="21" t="n">
+        <v>109.045</v>
+      </c>
+      <c r="G107" s="21" t="n">
+        <v>108.915</v>
+      </c>
+      <c r="H107" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="I107" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.74)</t>
+        </is>
+      </c>
+      <c r="K107" s="13" t="n">
+        <v>996.42</v>
+      </c>
+      <c r="L107" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M107" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N107" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="10" t="inlineStr">
+        <is>
+          <t>ETHUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B108" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:28:12</t>
+        </is>
+      </c>
+      <c r="C108" s="10" t="inlineStr">
+        <is>
+          <t>ETHUSDT</t>
+        </is>
+      </c>
+      <c r="D108" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E108" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F108" s="21" t="n">
+        <v>2478.635</v>
+      </c>
+      <c r="G108" s="21" t="n">
+        <v>2478.575</v>
+      </c>
+      <c r="H108" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.44)</t>
+        </is>
+      </c>
+      <c r="K108" s="13" t="n">
+        <v>996.25</v>
+      </c>
+      <c r="L108" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M108" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N108" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>AVAXUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B109" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:28:22</t>
+        </is>
+      </c>
+      <c r="C109" s="10" t="inlineStr">
+        <is>
+          <t>AVAXUSDT</t>
+        </is>
+      </c>
+      <c r="D109" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E109" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F109" s="21" t="n">
+        <v>10.1905</v>
+      </c>
+      <c r="G109" s="21" t="n">
+        <v>10.1865</v>
+      </c>
+      <c r="H109" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I109" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.76)</t>
+        </is>
+      </c>
+      <c r="K109" s="13" t="n">
+        <v>996.12</v>
+      </c>
+      <c r="L109" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M109" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="N109" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="10" t="inlineStr">
+        <is>
+          <t>AVAXUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B110" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:28:22</t>
+        </is>
+      </c>
+      <c r="C110" s="10" t="inlineStr">
+        <is>
+          <t>AVAXUSDT</t>
+        </is>
+      </c>
+      <c r="D110" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E110" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F110" s="21" t="n">
+        <v>10.1965</v>
+      </c>
+      <c r="G110" s="21" t="n">
+        <v>10.1865</v>
+      </c>
+      <c r="H110" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="I110" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.76)</t>
+        </is>
+      </c>
+      <c r="K110" s="13" t="n">
+        <v>996.03</v>
+      </c>
+      <c r="L110" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M110" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N110" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="10" t="inlineStr">
+        <is>
+          <t>DOTUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B111" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:28:30</t>
+        </is>
+      </c>
+      <c r="C111" s="10" t="inlineStr">
+        <is>
+          <t>DOTUSDT</t>
+        </is>
+      </c>
+      <c r="D111" s="10" t="inlineStr">
+        <is>
+          <t>🟢 LONG</t>
+        </is>
+      </c>
+      <c r="E111" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F111" s="21" t="n">
+        <v>1.21665</v>
+      </c>
+      <c r="G111" s="21" t="n">
+        <v>1.21415</v>
+      </c>
+      <c r="H111" s="22" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="I111" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (-0.52)</t>
+        </is>
+      </c>
+      <c r="K111" s="13" t="n">
+        <v>995.78</v>
+      </c>
+      <c r="L111" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M111" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="N111" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="10" t="inlineStr">
+        <is>
+          <t>AVAXUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B112" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:28:31</t>
+        </is>
+      </c>
+      <c r="C112" s="10" t="inlineStr">
+        <is>
+          <t>AVAXUSDT</t>
+        </is>
+      </c>
+      <c r="D112" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E112" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F112" s="21" t="n">
+        <v>10.1945</v>
+      </c>
+      <c r="G112" s="21" t="n">
+        <v>10.1865</v>
+      </c>
+      <c r="H112" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I112" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.52)</t>
+        </is>
+      </c>
+      <c r="K112" s="13" t="n">
+        <v>995.63</v>
+      </c>
+      <c r="L112" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M112" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N112" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="10" t="inlineStr">
+        <is>
+          <t>INJUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B113" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:28:53</t>
+        </is>
+      </c>
+      <c r="C113" s="10" t="inlineStr">
+        <is>
+          <t>INJUSDT</t>
+        </is>
+      </c>
+      <c r="D113" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E113" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F113" s="21" t="n">
+        <v>6.8795</v>
+      </c>
+      <c r="G113" s="21" t="n">
+        <v>6.8725</v>
+      </c>
+      <c r="H113" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I113" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.70)</t>
+        </is>
+      </c>
+      <c r="K113" s="13" t="n">
+        <v>994.29</v>
+      </c>
+      <c r="L113" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M113" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N113" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="10" t="inlineStr">
+        <is>
+          <t>OPUSDT_1791577</t>
+        </is>
+      </c>
+      <c r="B114" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:29:01</t>
+        </is>
+      </c>
+      <c r="C114" s="10" t="inlineStr">
+        <is>
+          <t>OPUSDT</t>
+        </is>
+      </c>
+      <c r="D114" s="10" t="inlineStr">
+        <is>
+          <t>🟢 LONG</t>
+        </is>
+      </c>
+      <c r="E114" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F114" s="21" t="n">
+        <v>0.127205</v>
+      </c>
+      <c r="G114" s="21" t="n">
+        <v>0.126345</v>
+      </c>
+      <c r="H114" s="22" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="I114" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (-0.68)</t>
+        </is>
+      </c>
+      <c r="K114" s="13" t="n">
+        <v>994.64</v>
+      </c>
+      <c r="L114" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M114" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N114" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="10" t="inlineStr">
+        <is>
+          <t>WIFUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B115" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:29:41</t>
+        </is>
+      </c>
+      <c r="C115" s="10" t="inlineStr">
+        <is>
+          <t>WIFUSDT</t>
+        </is>
+      </c>
+      <c r="D115" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E115" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F115" s="21" t="n">
+        <v>0.21085</v>
+      </c>
+      <c r="G115" s="21" t="n">
+        <v>0.21035</v>
+      </c>
+      <c r="H115" s="5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="I115" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.69)</t>
+        </is>
+      </c>
+      <c r="K115" s="13" t="n">
+        <v>994.08</v>
+      </c>
+      <c r="L115" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M115" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N115" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="10" t="inlineStr">
+        <is>
+          <t>OPUSDT_1791577</t>
+        </is>
+      </c>
+      <c r="B116" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:29:49</t>
+        </is>
+      </c>
+      <c r="C116" s="10" t="inlineStr">
+        <is>
+          <t>OPUSDT</t>
+        </is>
+      </c>
+      <c r="D116" s="10" t="inlineStr">
+        <is>
+          <t>🟢 LONG</t>
+        </is>
+      </c>
+      <c r="E116" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F116" s="21" t="n">
+        <v>0.126915</v>
+      </c>
+      <c r="G116" s="21" t="n">
+        <v>0.126285</v>
+      </c>
+      <c r="H116" s="22" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="I116" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (-0.47)</t>
+        </is>
+      </c>
+      <c r="K116" s="13" t="n">
+        <v>993.88</v>
+      </c>
+      <c r="L116" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M116" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N116" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="10" t="inlineStr">
+        <is>
+          <t>OPUSDT_1791577</t>
+        </is>
+      </c>
+      <c r="B117" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:30:30</t>
+        </is>
+      </c>
+      <c r="C117" s="10" t="inlineStr">
+        <is>
+          <t>OPUSDT</t>
+        </is>
+      </c>
+      <c r="D117" s="10" t="inlineStr">
+        <is>
+          <t>🟢 LONG</t>
+        </is>
+      </c>
+      <c r="E117" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F117" s="21" t="n">
+        <v>0.126545</v>
+      </c>
+      <c r="G117" s="21" t="n">
+        <v>0.126275</v>
+      </c>
+      <c r="H117" s="22" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="I117" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (-0.47)</t>
+        </is>
+      </c>
+      <c r="K117" s="13" t="n">
+        <v>993.79</v>
+      </c>
+      <c r="L117" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M117" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="N117" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="10" t="inlineStr">
+        <is>
+          <t>ADAUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B118" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:31:42</t>
+        </is>
+      </c>
+      <c r="C118" s="10" t="inlineStr">
+        <is>
+          <t>ADAUSDT</t>
+        </is>
+      </c>
+      <c r="D118" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E118" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F118" s="21" t="n">
+        <v>0.23665</v>
+      </c>
+      <c r="G118" s="21" t="n">
+        <v>0.23645</v>
+      </c>
+      <c r="H118" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I118" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>PROFIT PROTECT (giveback)</t>
+        </is>
+      </c>
+      <c r="K118" s="13" t="n">
+        <v>999.6799999999999</v>
+      </c>
+      <c r="L118" s="10" t="inlineStr">
+        <is>
+          <t>🛡️ YES</t>
+        </is>
+      </c>
+      <c r="M118" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="N118" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="10" t="inlineStr">
+        <is>
+          <t>NEARUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B119" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:32:31</t>
+        </is>
+      </c>
+      <c r="C119" s="10" t="inlineStr">
+        <is>
+          <t>NEARUSDT</t>
+        </is>
+      </c>
+      <c r="D119" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E119" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F119" s="21" t="n">
+        <v>4.6635</v>
+      </c>
+      <c r="G119" s="21" t="n">
+        <v>4.6585</v>
+      </c>
+      <c r="H119" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I119" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>PROFIT PROTECT (giveback)</t>
+        </is>
+      </c>
+      <c r="K119" s="13" t="n">
+        <v>999.6</v>
+      </c>
+      <c r="L119" s="10" t="inlineStr">
+        <is>
+          <t>🛡️ YES</t>
+        </is>
+      </c>
+      <c r="M119" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N119" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="10" t="inlineStr">
+        <is>
+          <t>TIAUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B120" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:32:45</t>
+        </is>
+      </c>
+      <c r="C120" s="10" t="inlineStr">
+        <is>
+          <t>TIAUSDT</t>
+        </is>
+      </c>
+      <c r="D120" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E120" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F120" s="21" t="n">
+        <v>0.46625</v>
+      </c>
+      <c r="G120" s="21" t="n">
+        <v>0.46585</v>
+      </c>
+      <c r="H120" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I120" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>PROFIT PROTECT (giveback)</t>
+        </is>
+      </c>
+      <c r="K120" s="13" t="n">
+        <v>999.53</v>
+      </c>
+      <c r="L120" s="10" t="inlineStr">
+        <is>
+          <t>🛡️ YES</t>
+        </is>
+      </c>
+      <c r="M120" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="N120" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="10" t="inlineStr">
+        <is>
+          <t>SUIUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B121" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:33:03</t>
+        </is>
+      </c>
+      <c r="C121" s="10" t="inlineStr">
+        <is>
+          <t>SUIUSDT</t>
+        </is>
+      </c>
+      <c r="D121" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E121" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F121" s="21" t="n">
+        <v>1.05695</v>
+      </c>
+      <c r="G121" s="21" t="n">
+        <v>1.05615</v>
+      </c>
+      <c r="H121" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I121" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.86)</t>
+        </is>
+      </c>
+      <c r="K121" s="13" t="n">
+        <v>999.47</v>
+      </c>
+      <c r="L121" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M121" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N121" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="10" t="inlineStr">
+        <is>
+          <t>ARBUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B122" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:33:34</t>
+        </is>
+      </c>
+      <c r="C122" s="10" t="inlineStr">
+        <is>
+          <t>ARBUSDT</t>
+        </is>
+      </c>
+      <c r="D122" s="10" t="inlineStr">
+        <is>
+          <t>🟢 LONG</t>
+        </is>
+      </c>
+      <c r="E122" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F122" s="21" t="n">
+        <v>0.179405</v>
+      </c>
+      <c r="G122" s="21" t="n">
+        <v>0.179685</v>
+      </c>
+      <c r="H122" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I122" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (-0.79)</t>
+        </is>
+      </c>
+      <c r="K122" s="13" t="n">
+        <v>999.38</v>
+      </c>
+      <c r="L122" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M122" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N122" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="10" t="inlineStr">
+        <is>
+          <t>RENDERUSDT_179</t>
+        </is>
+      </c>
+      <c r="B123" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:33:36</t>
+        </is>
+      </c>
+      <c r="C123" s="10" t="inlineStr">
+        <is>
+          <t>RENDERUSDT</t>
+        </is>
+      </c>
+      <c r="D123" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E123" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F123" s="21" t="n">
+        <v>1.8465</v>
+      </c>
+      <c r="G123" s="21" t="n">
+        <v>1.8475</v>
+      </c>
+      <c r="H123" s="22" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="I123" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.87)</t>
+        </is>
+      </c>
+      <c r="K123" s="13" t="n">
+        <v>999.3099999999999</v>
+      </c>
+      <c r="L123" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M123" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N123" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="10" t="inlineStr">
+        <is>
+          <t>AAVEUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B124" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:33:41</t>
+        </is>
+      </c>
+      <c r="C124" s="10" t="inlineStr">
+        <is>
+          <t>AAVEUSDT</t>
+        </is>
+      </c>
+      <c r="D124" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E124" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F124" s="21" t="n">
+        <v>166.615</v>
+      </c>
+      <c r="G124" s="21" t="n">
+        <v>166.715</v>
+      </c>
+      <c r="H124" s="22" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="I124" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.69)</t>
+        </is>
+      </c>
+      <c r="K124" s="13" t="n">
+        <v>999.09</v>
+      </c>
+      <c r="L124" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M124" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="N124" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="10" t="inlineStr">
+        <is>
+          <t>BNBUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B125" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:34:07</t>
+        </is>
+      </c>
+      <c r="C125" s="10" t="inlineStr">
+        <is>
+          <t>BNBUSDT</t>
+        </is>
+      </c>
+      <c r="D125" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E125" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F125" s="21" t="n">
+        <v>738.775</v>
+      </c>
+      <c r="G125" s="21" t="n">
+        <v>739.005</v>
+      </c>
+      <c r="H125" s="22" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="I125" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.64)</t>
+        </is>
+      </c>
+      <c r="K125" s="13" t="n">
+        <v>998.36</v>
+      </c>
+      <c r="L125" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M125" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="N125" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="10" t="inlineStr">
+        <is>
+          <t>OPUSDT_1791578</t>
+        </is>
+      </c>
+      <c r="B126" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:34:08</t>
+        </is>
+      </c>
+      <c r="C126" s="10" t="inlineStr">
+        <is>
+          <t>OPUSDT</t>
+        </is>
+      </c>
+      <c r="D126" s="10" t="inlineStr">
+        <is>
+          <t>🟢 LONG</t>
+        </is>
+      </c>
+      <c r="E126" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F126" s="21" t="n">
+        <v>0.125905</v>
+      </c>
+      <c r="G126" s="21" t="n">
+        <v>0.126165</v>
+      </c>
+      <c r="H126" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I126" s="10" t="inlineStr">
+        <is>
+          <t>🟢 WIN</t>
+        </is>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (-0.61)</t>
+        </is>
+      </c>
+      <c r="K126" s="13" t="n">
+        <v>998.26</v>
+      </c>
+      <c r="L126" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M126" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N126" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="10" t="inlineStr">
+        <is>
+          <t>NEARUSDT_17915</t>
+        </is>
+      </c>
+      <c r="B127" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:34:14</t>
+        </is>
+      </c>
+      <c r="C127" s="10" t="inlineStr">
+        <is>
+          <t>NEARUSDT</t>
+        </is>
+      </c>
+      <c r="D127" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E127" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F127" s="21" t="n">
+        <v>4.656499999999999</v>
+      </c>
+      <c r="G127" s="21" t="n">
+        <v>4.6685</v>
+      </c>
+      <c r="H127" s="22" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="I127" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.77)</t>
+        </is>
+      </c>
+      <c r="K127" s="13" t="n">
+        <v>998.13</v>
+      </c>
+      <c r="L127" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M127" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N127" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="10" t="inlineStr">
+        <is>
+          <t>BTCUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B128" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:34:28</t>
+        </is>
+      </c>
+      <c r="C128" s="10" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="D128" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E128" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F128" s="21" t="n">
+        <v>82339.75</v>
+      </c>
+      <c r="G128" s="21" t="n">
+        <v>82356.25</v>
+      </c>
+      <c r="H128" s="22" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="I128" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.94)</t>
+        </is>
+      </c>
+      <c r="K128" s="13" t="n">
+        <v>997.65</v>
+      </c>
+      <c r="L128" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M128" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N128" s="10" t="inlineStr">
+        <is>
+          <t>PAPER SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="10" t="inlineStr">
+        <is>
+          <t>INJUSDT_179157</t>
+        </is>
+      </c>
+      <c r="B129" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:34:42</t>
+        </is>
+      </c>
+      <c r="C129" s="10" t="inlineStr">
+        <is>
+          <t>INJUSDT</t>
+        </is>
+      </c>
+      <c r="D129" s="10" t="inlineStr">
+        <is>
+          <t>🔴 SHORT</t>
+        </is>
+      </c>
+      <c r="E129" s="10" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F129" s="21" t="n">
+        <v>6.8655</v>
+      </c>
+      <c r="G129" s="21" t="n">
+        <v>6.8695</v>
+      </c>
+      <c r="H129" s="22" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="I129" s="10" t="inlineStr">
+        <is>
+          <t>🔴 LOSS</t>
+        </is>
+      </c>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>OFI ADVERSE REVERSAL (+0.46)</t>
+        </is>
+      </c>
+      <c r="K129" s="13" t="n">
+        <v>997.26</v>
+      </c>
+      <c r="L129" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M129" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="N129" s="10" t="inlineStr">
         <is>
           <t>PAPER SIMULATOR</t>
         </is>
